--- a/02_Requirements Roadmap & Milestones/Requirements SNOMED_CT Implementation Roadmap V1 092026.xlsx
+++ b/02_Requirements Roadmap & Milestones/Requirements SNOMED_CT Implementation Roadmap V1 092026.xlsx
@@ -6,12 +6,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcloudbelgium-my.sharepoint.com/personal/veronique_deleeuw_health_fgov_be/Documents/Documents/FOD VVVL/00 SNOMED_CT integratie/Requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcloudbelgium-my.sharepoint.com/personal/beau_declercq_health_fgov_be/Documents/Documents/GitHub/sct_implementation/02_Requirements Roadmap &amp; Milestones/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="12" documentId="8_{65BE4FBC-4BC4-40F7-BC08-681DED31C051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC144D6D-7518-4FFA-967E-132ACB726B6C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5D9F650B-E967-418B-8CE1-28BF1D198818}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5D9F650B-E967-418B-8CE1-28BF1D198818}"/>
   </bookViews>
   <sheets>
     <sheet name="eHR Reqs list" sheetId="7" r:id="rId1"/>
@@ -2066,7 +2066,7 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{45E2B2EF-6F82-4547-B29D-82B403865718}">
           <x14:formula1>
             <xm:f>'dropdown coding'!$B$15:$B$19</xm:f>
@@ -2231,6 +2231,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db1ec342-b0c0-44cc-b0c8-6e5000eb27a9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="49b5624a-53ae-46bd-85da-48f591460cf9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C568600A10F9D042A4C8C50199885130" ma:contentTypeVersion="13" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="888c4edcfa65588c4b57e3656d2b892c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3519ed71-685b-4080-8187-34ed5e74e3fe" xmlns:ns3="53c7e4a9-e3b3-4376-a159-1a6438f3d749" xmlns:ns4="db1ec342-b0c0-44cc-b0c8-6e5000eb27a9" xmlns:ns5="9a87d615-fc3c-40a2-8879-2661543bcefa" xmlns:ns6="49b5624a-53ae-46bd-85da-48f591460cf9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54c91cca29da15e9dd208e0bc0fa96d6" ns2:_="" ns3:_="" ns4:_="" ns5:_="" ns6:_="">
     <xsd:import namespace="3519ed71-685b-4080-8187-34ed5e74e3fe"/>
@@ -2494,44 +2514,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="db1ec342-b0c0-44cc-b0c8-6e5000eb27a9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="49b5624a-53ae-46bd-85da-48f591460cf9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1099EBD-CEC7-4226-9945-0B20290D1CFB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5595F6B8-4EF7-4B6B-97B7-A3E700623138}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3519ed71-685b-4080-8187-34ed5e74e3fe"/>
-    <ds:schemaRef ds:uri="53c7e4a9-e3b3-4376-a159-1a6438f3d749"/>
-    <ds:schemaRef ds:uri="db1ec342-b0c0-44cc-b0c8-6e5000eb27a9"/>
-    <ds:schemaRef ds:uri="9a87d615-fc3c-40a2-8879-2661543bcefa"/>
-    <ds:schemaRef ds:uri="49b5624a-53ae-46bd-85da-48f591460cf9"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2557,9 +2543,23 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5595F6B8-4EF7-4B6B-97B7-A3E700623138}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1099EBD-CEC7-4226-9945-0B20290D1CFB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3519ed71-685b-4080-8187-34ed5e74e3fe"/>
+    <ds:schemaRef ds:uri="53c7e4a9-e3b3-4376-a159-1a6438f3d749"/>
+    <ds:schemaRef ds:uri="db1ec342-b0c0-44cc-b0c8-6e5000eb27a9"/>
+    <ds:schemaRef ds:uri="9a87d615-fc3c-40a2-8879-2661543bcefa"/>
+    <ds:schemaRef ds:uri="49b5624a-53ae-46bd-85da-48f591460cf9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
